--- a/artfynd/A 15262-2026 artfynd.xlsx
+++ b/artfynd/A 15262-2026 artfynd.xlsx
@@ -675,55 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16081282</v>
+        <v>78716362</v>
       </c>
       <c r="B2" t="n">
-        <v>99611</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221343</v>
+        <v>219847</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brunklöver</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Trifolium spadiceum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Silvtjärn, 2,5 km NV om, Vstm</t>
+          <t>Borrmossen, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546094.7374965381</v>
+        <v>546047</v>
       </c>
       <c r="R2" t="n">
-        <v>6661476.473370632</v>
+        <v>6661803</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2014-07-05</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-06-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2014-07-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-06-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,38 +758,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>vägkant</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bo Eriksson</t>
+          <t>Emil Persson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bo Eriksson</t>
+          <t>Emil Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>78716366</v>
+        <v>16081282</v>
       </c>
       <c r="B3" t="n">
-        <v>99611</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102464</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,20 +806,21 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Borrmossen, Vstm</t>
+          <t>Silvtjärn, 2,5 km NV om, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546047.1644968122</v>
+        <v>546095</v>
       </c>
       <c r="R3" t="n">
-        <v>6661803.172256001</v>
+        <v>6661476</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,22 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-06-29</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-07-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-06-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-07-05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,56 +861,55 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>vägkant</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Emil Persson</t>
+          <t>Bo Eriksson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Emil Persson</t>
+          <t>Bo Eriksson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>78716362</v>
+        <v>78716366</v>
       </c>
       <c r="B4" t="n">
-        <v>96356</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102464</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219847</v>
+        <v>221343</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brunklöver</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Trifolium spadiceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -958,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546047.1644968122</v>
+        <v>546047</v>
       </c>
       <c r="R4" t="n">
-        <v>6661803.172256001</v>
+        <v>6661803</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,19 +956,9 @@
           <t>2019-06-29</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-06-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 15262-2026 artfynd.xlsx
+++ b/artfynd/A 15262-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78716362</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16081282</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,8 +998,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78716366</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>